--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,766 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.6425,0.2263,0.0225,0.0351</t>
-  </si>
-  <si>
-    <t>0.0017,0.0007,0.0000,0.9992</t>
-  </si>
-  <si>
-    <t>0.9471,0.0239,0.0022,0.0076</t>
-  </si>
-  <si>
-    <t>0.0176,0.0061,0.0025,0.9874</t>
-  </si>
-  <si>
-    <t>0.9244,0.1347,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9693,0.0651,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.8618,0.2634,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9729,0.0530,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9198,0.1535,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8305,0.3110,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9891,0.0191,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9125,0.1595,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.5804,0.1019,0.2460,0.0097</t>
-  </si>
-  <si>
-    <t>0.0109,0.0384,0.9714,0.0004</t>
-  </si>
-  <si>
-    <t>0.0023,0.1091,0.9861,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.0682,0.9798,0.0004</t>
-  </si>
-  <si>
-    <t>0.2467,0.0322,0.7128,0.0068</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.1797,0.8101,0.0189,0.0189</t>
+  </si>
+  <si>
+    <t>0.0019,0.0011,0.0000,0.9990</t>
+  </si>
+  <si>
+    <t>0.8414,0.0260,0.0016,0.0473</t>
+  </si>
+  <si>
+    <t>0.0406,0.0143,0.0101,0.9631</t>
+  </si>
+  <si>
+    <t>0.7833,0.3404,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9642,0.0743,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7832,0.3685,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9768,0.0443,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9241,0.1446,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6126,0.5612,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.9809,0.0416,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8917,0.2226,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8338,0.0330,0.0870,0.0067</t>
+  </si>
+  <si>
+    <t>0.0006,0.1917,0.9916,0.0001</t>
+  </si>
+  <si>
+    <t>0.0139,0.2187,0.9136,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.0296,0.9956,0.0001</t>
+  </si>
+  <si>
+    <t>0.6684,0.2119,0.0451,0.0062</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9984,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0005,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9998,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9996,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.9956,0.0071,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2423,0.0074,0.7488,0.0021</t>
-  </si>
-  <si>
-    <t>0.1087,0.0479,0.8147,0.0007</t>
-  </si>
-  <si>
-    <t>0.0057,0.0026,0.9921,0.0001</t>
-  </si>
-  <si>
-    <t>0.0127,0.0254,0.9688,0.0003</t>
-  </si>
-  <si>
-    <t>0.0047,0.0060,0.9918,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.0029,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0036,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0045,0.9942,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0741,0.7542,0.1899,0.0012</t>
-  </si>
-  <si>
-    <t>0.0020,0.0261,0.9924,0.0031</t>
-  </si>
-  <si>
-    <t>0.0025,0.9805,0.1014,0.0001</t>
-  </si>
-  <si>
-    <t>0.5404,0.2738,0.1377,0.0082</t>
-  </si>
-  <si>
-    <t>0.0365,0.5282,0.6785,0.0018</t>
-  </si>
-  <si>
-    <t>0.0203,0.9796,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9886,0.3911,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9665,0.7469,0.0001</t>
-  </si>
-  <si>
-    <t>0.0023,0.0259,0.9909,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.1356,0.9879,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.0093,0.9893,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.2688,0.9794,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0058,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0305,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.5497,0.0033,0.9619</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0065,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0025,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3097,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.2356,0.9913,0.0000</t>
-  </si>
-  <si>
-    <t>0.0084,0.0094,0.9843,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.0073,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0796,0.9913,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.1136,0.9577,0.0004</t>
-  </si>
-  <si>
-    <t>0.1458,0.8930,0.0060,0.0002</t>
-  </si>
-  <si>
-    <t>0.7899,0.2409,0.0066,0.0009</t>
-  </si>
-  <si>
-    <t>0.0853,0.9303,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.2234,0.9931,0.0003</t>
-  </si>
-  <si>
-    <t>0.2019,0.8581,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.8752,0.1952,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.0564,0.9543,0.0069,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9552,0.9244,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.4770,0.9865,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.0941,0.9855,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9804,0.9756,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0646,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0021,0.0000</t>
+    <t>0.6118,0.0336,0.3270,0.0163</t>
+  </si>
+  <si>
+    <t>0.0661,0.0250,0.8916,0.0013</t>
+  </si>
+  <si>
+    <t>0.0015,0.0319,0.9935,0.0001</t>
+  </si>
+  <si>
+    <t>0.0045,0.0303,0.9832,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0055,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0101,0.0051,0.9853,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0012,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.9964,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.1263,0.8059,0.0639,0.0016</t>
+  </si>
+  <si>
+    <t>0.0012,0.0450,0.9935,0.0026</t>
+  </si>
+  <si>
+    <t>0.0082,0.9741,0.0403,0.0004</t>
+  </si>
+  <si>
+    <t>0.6337,0.3149,0.0386,0.0064</t>
+  </si>
+  <si>
+    <t>0.3162,0.6831,0.0237,0.0081</t>
+  </si>
+  <si>
+    <t>0.0276,0.9745,0.0037,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.9915,0.0251,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9763,0.7351,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0118,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.0088,0.1114,0.9470,0.0004</t>
+  </si>
+  <si>
+    <t>0.0076,0.0020,0.9894,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.4209,0.9882,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9944,0.0339,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0277,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.2680,0.0063,0.9802</t>
+  </si>
+  <si>
+    <t>0.0002,0.9980,0.0026,0.0016</t>
+  </si>
+  <si>
+    <t>0.0002,0.9986,0.0107,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.4180,0.9793,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.5788,0.9598,0.0001</t>
+  </si>
+  <si>
+    <t>0.0079,0.0040,0.9879,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.0106,0.9968,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0172,0.9934,0.0002</t>
+  </si>
+  <si>
+    <t>0.0013,0.3394,0.9772,0.0002</t>
+  </si>
+  <si>
+    <t>0.0369,0.9698,0.0034,0.0001</t>
+  </si>
+  <si>
+    <t>0.8320,0.2182,0.0046,0.0005</t>
+  </si>
+  <si>
+    <t>0.3372,0.7710,0.0046,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.5871,0.9841,0.0001</t>
+  </si>
+  <si>
+    <t>0.6367,0.4821,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.7136,0.3894,0.0041,0.0005</t>
+  </si>
+  <si>
+    <t>0.1137,0.9081,0.0103,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9761,0.8174,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.2980,0.9840,0.0000</t>
+  </si>
+  <si>
+    <t>0.0050,0.2136,0.9432,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9633,0.9712,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0156,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9987,0.0019,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0952,0.2448,0.6944,0.0024</t>
-  </si>
-  <si>
-    <t>0.0330,0.0962,0.9076,0.0020</t>
-  </si>
-  <si>
-    <t>0.0003,0.0364,0.9985,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9917,0.9240,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.9190,0.5887,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9976,0.4050,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9879,0.8342,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.0102,0.9969</t>
+    <t>0.7506,0.0455,0.1552,0.0045</t>
+  </si>
+  <si>
+    <t>0.2288,0.4673,0.2214,0.0036</t>
+  </si>
+  <si>
+    <t>0.0002,0.1386,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9873,0.8375,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9577,0.7941,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9960,0.3137,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9967,0.8271,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0003,0.0340,0.9952</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.0004,0.9997</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.0011,0.9988</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9835,0.8684,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9729,0.9532,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9489,0.9341,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.7997,0.9339,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9896,0.8763,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9294,0.9077,0.0000</t>
+  </si>
+  <si>
+    <t>0.9641,0.0809,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.5274,0.6362,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.5625,0.6096,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.9870,0.0202,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.4029,0.7367,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.4272,0.7375,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.7262,0.3524,0.0045,0.0005</t>
+  </si>
+  <si>
+    <t>0.7297,0.4333,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9931,0.0114,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9731,0.0590,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9940,0.0121,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9488,0.0842,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.8440,0.2653,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9706,0.0614,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8517,0.2210,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9660,0.0488,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0016,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0068,0.0819,0.9663,0.0004</t>
+  </si>
+  <si>
+    <t>0.7134,0.0073,0.3388,0.0055</t>
+  </si>
+  <si>
+    <t>0.0172,0.0020,0.9816,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9989,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9982,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9990,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.9937,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.1438,0.1643,0.6337,0.0058</t>
+  </si>
+  <si>
+    <t>0.0091,0.0184,0.9795,0.0003</t>
+  </si>
+  <si>
+    <t>0.0834,0.2028,0.6627,0.0108</t>
+  </si>
+  <si>
+    <t>0.1738,0.0299,0.7622,0.0060</t>
+  </si>
+  <si>
+    <t>0.0208,0.2481,0.0078,0.9166</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9983,0.0017,0.0036</t>
+  </si>
+  <si>
+    <t>0.0000,0.9964,0.9762,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9980,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.0058,0.9926,0.0027,0.0000</t>
+  </si>
+  <si>
+    <t>0.0149,0.9848,0.0030,0.0000</t>
+  </si>
+  <si>
+    <t>0.7922,0.2812,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.8516,0.2052,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.8062,0.2415,0.0040,0.0011</t>
+  </si>
+  <si>
+    <t>0.9553,0.0405,0.0041,0.0018</t>
+  </si>
+  <si>
+    <t>0.9693,0.0448,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.3488,0.7235,0.0090,0.0005</t>
+  </si>
+  <si>
+    <t>0.9375,0.0898,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.8989,0.1459,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.4822,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7871,0.9879,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.3692,0.9886,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.1618,0.9819,0.0001</t>
+  </si>
+  <si>
+    <t>0.7340,0.1017,0.0691,0.0137</t>
+  </si>
+  <si>
+    <t>0.2938,0.0638,0.5824,0.0102</t>
+  </si>
+  <si>
+    <t>0.0195,0.0171,0.9632,0.0020</t>
+  </si>
+  <si>
+    <t>0.1619,0.8049,0.0359,0.0106</t>
+  </si>
+  <si>
+    <t>0.2559,0.0006,0.0010,0.8623</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.0007,0.9995</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.0012,0.9993</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0002,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.9708,0.8385,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9581,0.9104,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9799,0.9691,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9649,0.6601,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9873,0.9395,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9408,0.9744,0.0000</t>
-  </si>
-  <si>
-    <t>0.5231,0.6704,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.8639,0.2600,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.6284,0.5702,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9524,0.0846,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.3065,0.8096,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.8360,0.2932,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.6389,0.4672,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.9016,0.2108,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9877,0.0182,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.8414,0.3004,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9910,0.0155,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9551,0.0881,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.8699,0.2319,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9634,0.0704,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9621,0.0586,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9583,0.0652,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.0995,0.9684,0.0003</t>
-  </si>
-  <si>
-    <t>0.7925,0.0032,0.2576,0.0043</t>
-  </si>
-  <si>
-    <t>0.0702,0.0022,0.9369,0.0002</t>
-  </si>
-  <si>
-    <t>0.0011,0.9981,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9988,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9992,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0039,0.9939,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.2020,0.1786,0.5334,0.0067</t>
-  </si>
-  <si>
-    <t>0.0694,0.0129,0.9117,0.0012</t>
-  </si>
-  <si>
-    <t>0.0457,0.7350,0.2918,0.0063</t>
-  </si>
-  <si>
-    <t>0.0951,0.0649,0.8087,0.0060</t>
-  </si>
-  <si>
-    <t>0.0128,0.0192,0.0205,0.9671</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.9958,0.9780,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9988,0.0019,0.0000</t>
-  </si>
-  <si>
-    <t>0.0293,0.9618,0.0145,0.0001</t>
-  </si>
-  <si>
-    <t>0.0122,0.9868,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.8659,0.1961,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9264,0.1069,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9349,0.0841,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.7552,0.2771,0.0091,0.0019</t>
-  </si>
-  <si>
-    <t>0.8793,0.1878,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.4036,0.6714,0.0110,0.0004</t>
-  </si>
-  <si>
-    <t>0.9856,0.0220,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9855,0.0167,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.8234,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8733,0.9842,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3533,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.0845,0.9822,0.0001</t>
-  </si>
-  <si>
-    <t>0.7213,0.0384,0.1908,0.0168</t>
-  </si>
-  <si>
-    <t>0.3292,0.1267,0.4323,0.0144</t>
-  </si>
-  <si>
-    <t>0.0233,0.0016,0.9771,0.0004</t>
-  </si>
-  <si>
-    <t>0.1625,0.7833,0.0412,0.0217</t>
-  </si>
-  <si>
-    <t>0.0490,0.0003,0.0005,0.9759</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.0002,0.9994</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.8146,0.0000</t>
-  </si>
-  <si>
-    <t>0.8211,0.2284,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.1231,0.8738,0.0231,0.0049</t>
-  </si>
-  <si>
-    <t>0.8919,0.1255,0.0034,0.0014</t>
-  </si>
-  <si>
-    <t>0.0230,0.9769,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.9731,0.0175,0.0024,0.0027</t>
-  </si>
-  <si>
-    <t>0.8191,0.0178,0.0013,0.0888</t>
-  </si>
-  <si>
-    <t>0.9740,0.0194,0.0031,0.0016</t>
-  </si>
-  <si>
-    <t>0.0017,0.0946,0.9895,0.0010</t>
-  </si>
-  <si>
-    <t>0.9733,0.0022,0.0023,0.0104</t>
-  </si>
-  <si>
-    <t>0.9699,0.0239,0.0036,0.0030</t>
-  </si>
-  <si>
-    <t>0.0019,0.9969,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.8339,0.1109,0.0161,0.0072</t>
-  </si>
-  <si>
-    <t>0.3816,0.6663,0.0077,0.0024</t>
-  </si>
-  <si>
-    <t>0.0072,0.9846,0.0149,0.0002</t>
-  </si>
-  <si>
-    <t>0.3461,0.6897,0.0089,0.0015</t>
-  </si>
-  <si>
-    <t>0.2660,0.7668,0.0110,0.0019</t>
-  </si>
-  <si>
-    <t>0.9838,0.0236,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9454,0.0825,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9513,0.0605,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.9929,0.0083,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.8372,0.2564,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.8353,0.2559,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9531,0.0679,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9747,0.0391,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.0383,0.9581,0.0085,0.0005</t>
-  </si>
-  <si>
-    <t>0.0221,0.9800,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.0399,0.9670,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.0091,0.7286,0.7576,0.0003</t>
-  </si>
-  <si>
-    <t>0.0149,0.9873,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.1765,0.8102,0.0239,0.0123</t>
-  </si>
-  <si>
-    <t>0.2547,0.8141,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.3587,0.7292,0.0058,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0832,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.1064,0.8435,0.0528,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0288,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1659,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0070,0.0152,0.9861,0.0002</t>
-  </si>
-  <si>
-    <t>0.0317,0.3354,0.7588,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.3770,0.9941,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0013,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0765,0.9948,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.2056,0.9752,0.0001</t>
-  </si>
-  <si>
-    <t>0.0263,0.0167,0.9588,0.0007</t>
-  </si>
-  <si>
-    <t>0.0156,0.6058,0.7629,0.0013</t>
-  </si>
-  <si>
-    <t>0.4837,0.3066,0.0983,0.0055</t>
-  </si>
-  <si>
-    <t>0.0055,0.6667,0.8265,0.0005</t>
-  </si>
-  <si>
-    <t>0.2290,0.6667,0.0767,0.0131</t>
-  </si>
-  <si>
-    <t>0.2541,0.1179,0.5418,0.0074</t>
-  </si>
-  <si>
-    <t>0.1081,0.3989,0.5313,0.0026</t>
-  </si>
-  <si>
-    <t>0.0019,0.9974,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0058,0.9940,0.0014,0.0000</t>
-  </si>
-  <si>
-    <t>0.0309,0.9762,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.1429,0.8961,0.0066,0.0006</t>
-  </si>
-  <si>
-    <t>0.0211,0.9833,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0230,0.9040,0.1260,0.0021</t>
-  </si>
-  <si>
-    <t>0.4393,0.0140,0.5622,0.0039</t>
-  </si>
-  <si>
-    <t>0.1959,0.5082,0.0718,0.1375</t>
-  </si>
-  <si>
-    <t>0.1374,0.1548,0.7060,0.0046</t>
-  </si>
-  <si>
-    <t>0.2927,0.0145,0.6669,0.0086</t>
-  </si>
-  <si>
-    <t>0.0010,0.0392,0.9954,0.0003</t>
-  </si>
-  <si>
-    <t>0.0094,0.0126,0.9810,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0713,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.2305,0.9596,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.6951,0.8481,0.0003</t>
-  </si>
-  <si>
-    <t>0.5251,0.6226,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.1347,0.9111,0.0036,0.0003</t>
-  </si>
-  <si>
-    <t>0.5496,0.5605,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.0877,0.9339,0.0065,0.0002</t>
-  </si>
-  <si>
-    <t>0.5715,0.5850,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.4285,0.6762,0.0038,0.0004</t>
-  </si>
-  <si>
-    <t>0.5088,0.5964,0.0062,0.0007</t>
-  </si>
-  <si>
-    <t>0.8431,0.2335,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.0064,0.1301,0.9732,0.0007</t>
-  </si>
-  <si>
-    <t>0.1078,0.8476,0.0525,0.0030</t>
-  </si>
-  <si>
-    <t>0.7944,0.0757,0.0370,0.0336</t>
-  </si>
-  <si>
-    <t>0.0005,0.0143,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0337,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.8576,0.9789,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0161,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.1174,0.9777,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0117,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.1571,0.9968,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.3411,0.9526,0.0005</t>
-  </si>
-  <si>
-    <t>0.3571,0.1387,0.3396,0.0127</t>
-  </si>
-  <si>
-    <t>0.5495,0.0029,0.5063,0.0015</t>
-  </si>
-  <si>
-    <t>0.8755,0.0144,0.0676,0.0076</t>
-  </si>
-  <si>
-    <t>0.6578,0.4683,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.0960,0.9381,0.0026,0.0000</t>
-  </si>
-  <si>
-    <t>0.9464,0.1078,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.5359,0.6245,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.8163,0.2074,0.0043,0.0018</t>
-  </si>
-  <si>
-    <t>0.4023,0.7565,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9373,0.1104,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.5293,0.5321,0.0095,0.0005</t>
-  </si>
-  <si>
-    <t>0.0119,0.0157,0.9774,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.1681,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.1659,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.3436,0.9614,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0084,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0844,0.0429,0.8508,0.0056</t>
-  </si>
-  <si>
-    <t>0.0008,0.2762,0.9863,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0062,0.9909,0.0002</t>
-  </si>
-  <si>
-    <t>0.9431,0.0155,0.0123,0.0073</t>
-  </si>
-  <si>
-    <t>0.0009,0.0016,0.0002,0.9994</t>
-  </si>
-  <si>
-    <t>0.0039,0.0003,0.0005,0.9976</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0001,0.9997</t>
-  </si>
-  <si>
-    <t>0.6263,0.0459,0.0037,0.1809</t>
+    <t>0.0001,0.0010,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0036,0.0005,0.0007,0.9975</t>
+  </si>
+  <si>
+    <t>0.0000,0.9956,0.9047,0.0000</t>
+  </si>
+  <si>
+    <t>0.5559,0.5243,0.0039,0.0019</t>
+  </si>
+  <si>
+    <t>0.0323,0.9664,0.0076,0.0013</t>
+  </si>
+  <si>
+    <t>0.9393,0.0713,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.0194,0.9782,0.0068,0.0002</t>
+  </si>
+  <si>
+    <t>0.9565,0.0480,0.0013,0.0015</t>
+  </si>
+  <si>
+    <t>0.6331,0.0133,0.0034,0.3050</t>
+  </si>
+  <si>
+    <t>0.9851,0.0122,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.0063,0.1537,0.9347,0.0120</t>
+  </si>
+  <si>
+    <t>0.9183,0.0038,0.0041,0.0430</t>
+  </si>
+  <si>
+    <t>0.9168,0.0710,0.0080,0.0043</t>
+  </si>
+  <si>
+    <t>0.0125,0.9851,0.0036,0.0002</t>
+  </si>
+  <si>
+    <t>0.6976,0.2433,0.0140,0.0084</t>
+  </si>
+  <si>
+    <t>0.1723,0.8575,0.0113,0.0023</t>
+  </si>
+  <si>
+    <t>0.0193,0.9762,0.0065,0.0005</t>
+  </si>
+  <si>
+    <t>0.1617,0.8684,0.0075,0.0007</t>
+  </si>
+  <si>
+    <t>0.2040,0.8286,0.0073,0.0019</t>
+  </si>
+  <si>
+    <t>0.8539,0.2012,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9518,0.0640,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9419,0.0731,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9907,0.0118,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.7890,0.3208,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.6639,0.4491,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.8986,0.1668,0.0010,0.0002</t>
+  </si>
+  <si>
+    <t>0.9687,0.0474,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0184,0.9789,0.0031,0.0006</t>
+  </si>
+  <si>
+    <t>0.0513,0.9603,0.0038,0.0001</t>
+  </si>
+  <si>
+    <t>0.0241,0.9775,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.0393,0.9015,0.0858,0.0004</t>
+  </si>
+  <si>
+    <t>0.0068,0.9927,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.2470,0.7547,0.0245,0.0036</t>
+  </si>
+  <si>
+    <t>0.1355,0.9018,0.0061,0.0003</t>
+  </si>
+  <si>
+    <t>0.1068,0.9206,0.0054,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.1163,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1372,0.8536,0.0288,0.0014</t>
+  </si>
+  <si>
+    <t>0.0000,0.1046,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.2919,0.9951,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.0158,0.9888,0.0002</t>
+  </si>
+  <si>
+    <t>0.0061,0.4382,0.8946,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.2109,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0154,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0365,0.9952,0.0001</t>
+  </si>
+  <si>
+    <t>0.0090,0.4793,0.8598,0.0005</t>
+  </si>
+  <si>
+    <t>0.0071,0.0872,0.9691,0.0004</t>
+  </si>
+  <si>
+    <t>0.0765,0.7744,0.1720,0.0050</t>
+  </si>
+  <si>
+    <t>0.0990,0.2446,0.6323,0.0024</t>
+  </si>
+  <si>
+    <t>0.0069,0.8255,0.5411,0.0003</t>
+  </si>
+  <si>
+    <t>0.5062,0.0522,0.4523,0.0077</t>
+  </si>
+  <si>
+    <t>0.6007,0.0908,0.2359,0.0127</t>
+  </si>
+  <si>
+    <t>0.0290,0.7648,0.3853,0.0011</t>
+  </si>
+  <si>
+    <t>0.0008,0.9986,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.9951,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0207,0.9820,0.0025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0355,0.9701,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.0040,0.9957,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0712,0.7377,0.2158,0.0055</t>
+  </si>
+  <si>
+    <t>0.8106,0.0050,0.2205,0.0047</t>
+  </si>
+  <si>
+    <t>0.4227,0.0728,0.3507,0.0413</t>
+  </si>
+  <si>
+    <t>0.3586,0.0354,0.6115,0.0055</t>
+  </si>
+  <si>
+    <t>0.3516,0.0219,0.5792,0.0124</t>
+  </si>
+  <si>
+    <t>0.0012,0.0343,0.9947,0.0004</t>
+  </si>
+  <si>
+    <t>0.0180,0.1076,0.9148,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.4285,0.9937,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.1766,0.9644,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.6321,0.9393,0.0001</t>
+  </si>
+  <si>
+    <t>0.8711,0.2317,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.4879,0.6598,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.5256,0.6052,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.4316,0.7331,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.3587,0.7585,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.7688,0.3517,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.4824,0.6075,0.0069,0.0012</t>
+  </si>
+  <si>
+    <t>0.8958,0.1407,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.2904,0.9915,0.0001</t>
+  </si>
+  <si>
+    <t>0.0641,0.9056,0.0393,0.0011</t>
+  </si>
+  <si>
+    <t>0.5705,0.2826,0.0498,0.0248</t>
+  </si>
+  <si>
+    <t>0.0006,0.0174,0.9980,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0767,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.7505,0.9789,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0315,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0866,0.9932,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0435,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.4124,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0063,0.0313,0.9807,0.0012</t>
+  </si>
+  <si>
+    <t>0.0685,0.3570,0.6278,0.0065</t>
+  </si>
+  <si>
+    <t>0.1127,0.0054,0.8909,0.0006</t>
+  </si>
+  <si>
+    <t>0.8734,0.0065,0.1207,0.0041</t>
+  </si>
+  <si>
+    <t>0.7739,0.2979,0.0048,0.0004</t>
+  </si>
+  <si>
+    <t>0.1510,0.9052,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.9336,0.1417,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.6690,0.4932,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.8653,0.1788,0.0015,0.0008</t>
+  </si>
+  <si>
+    <t>0.2713,0.8399,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.8190,0.2883,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.8048,0.2351,0.0066,0.0009</t>
+  </si>
+  <si>
+    <t>0.0115,0.0718,0.9504,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0667,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.2279,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.1090,0.9852,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0267,0.9954,0.0002</t>
+  </si>
+  <si>
+    <t>0.0918,0.0400,0.8477,0.0022</t>
+  </si>
+  <si>
+    <t>0.0030,0.2923,0.9630,0.0003</t>
+  </si>
+  <si>
+    <t>0.0042,0.0057,0.9919,0.0002</t>
+  </si>
+  <si>
+    <t>0.6390,0.2754,0.0056,0.0377</t>
+  </si>
+  <si>
+    <t>0.0009,0.0035,0.0009,0.9989</t>
+  </si>
+  <si>
+    <t>0.0271,0.0016,0.0009,0.9859</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.5511,0.0156,0.0016,0.3355</t>
   </si>
 </sst>
 </file>
@@ -1950,10 +1959,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2009,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2023,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2037,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2051,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2076,10 +2085,10 @@
         <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2093,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2107,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2174,10 +2183,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2191,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2247,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2258,10 +2267,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,7 +2382,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2387,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2426,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,7 +2452,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,7 +2480,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2541,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2566,10 +2575,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2597,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2611,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2636,10 +2645,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,7 +2718,7 @@
         <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,7 +2746,7 @@
         <v>262</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2748,10 +2757,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2762,10 +2771,10 @@
         <v>259</v>
       </c>
       <c r="C60" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2779,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,7 +2802,7 @@
         <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2863,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2891,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2902,10 +2911,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2916,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,7 +3110,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,7 +3138,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3168,10 +3177,10 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3182,10 +3191,10 @@
         <v>259</v>
       </c>
       <c r="C90" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3196,10 +3205,10 @@
         <v>259</v>
       </c>
       <c r="C91" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,7 +3236,7 @@
         <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3238,10 +3247,10 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3283,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3325,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3367,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3381,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3395,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3451,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,7 +3558,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3574,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3619,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3633,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,7 +3698,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,7 +3712,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3731,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3759,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3773,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3787,7 +3796,7 @@
         <v>262</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3801,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3826,10 +3835,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3896,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,7 +3936,7 @@
         <v>262</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>341</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4008,10 +4017,10 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,7 +4062,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4067,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,7 +4160,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4165,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,7 +4188,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,7 +4216,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,7 +4230,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4249,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4277,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4291,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,7 +4356,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,7 +4370,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4386,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,7 +4412,7 @@
         <v>262</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4417,7 +4426,7 @@
         <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,7 +4440,7 @@
         <v>262</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,7 +4454,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,7 +4482,7 @@
         <v>262</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4610,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4624,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,7 +4650,7 @@
         <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4652,10 +4661,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4666,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4680,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,7 +4706,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,7 +4734,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,7 +4748,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,7 +4762,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,7 +4776,7 @@
         <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4778,10 +4787,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4792,10 +4801,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,7 +4818,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,7 +4832,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,7 +4902,7 @@
         <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4904,10 +4913,10 @@
         <v>259</v>
       </c>
       <c r="C213" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,7 +4930,7 @@
         <v>262</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4932,10 +4941,10 @@
         <v>259</v>
       </c>
       <c r="C215" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,7 +4958,7 @@
         <v>262</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4963,7 +4972,7 @@
         <v>262</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4974,10 +4983,10 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,7 +5000,7 @@
         <v>262</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,7 +5042,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,7 +5098,7 @@
         <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5131,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5170,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,7 +5196,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,7 +5238,7 @@
         <v>262</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5254,10 +5263,10 @@
         <v>259</v>
       </c>
       <c r="C238" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5285,7 +5294,7 @@
         <v>262</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5299,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5310,10 +5319,10 @@
         <v>259</v>
       </c>
       <c r="C242" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>341</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
